--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_menu/lang_menu__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_menu/lang_menu__ui__part_0001.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Âm lượng hội thoại</t>
+          <t>Âm lượng Lời thoại</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Âm lượng hiệu ứng</t>
+          <t>Âm Lượng Hiệu Ứng</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Chất lượng kết cấu</t>
+          <t>Chất Lượng Họa Tiết</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Chế độ hiển thị</t>
+          <t>Chế độ Hiển thị</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Fullscreen</t>
+          <t>Toàn màn hình</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Windowed</t>
+          <t>Cửa Sổ</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Độ phân giải hiển thị</t>
+          <t>Độ phân giải Màn hình</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Độ phân giải hiển thị</t>
+          <t>Độ phân giải Màn hình</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Thiết Lập</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>30fps</t>
+          <t>30 FPS</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>60fps</t>
+          <t>60 FPS</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Chất lượng bóng đổ</t>
+          <t>Chất Lượng Bóng</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special</t>
+          <t>Hiệu Ứng Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Details kết cấu</t>
+          <t>Chi Tiết Họa Tiết</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Anti-Aliasing</t>
+          <t>Khử răng cưa</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Di chuyển tới trước</t>
+          <t>Tiến</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Move Backwards Lại</t>
+          <t>Lùi</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Move Sang Move Left</t>
+          <t>Trái</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Di chuyển sang phải</t>
+          <t>Phải</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Bật/Tắt đi bộ/chạy</t>
+          <t>Bật/Tắt Đi/Bộ</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Ctrl trái</t>
+          <t>Ctrl Trái</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Nhấp chuột trái</t>
+          <t>Nhấp Chuột Trái</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Lock mục tiêu</t>
+          <t>Khóa Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>Nút Chuột Giữa</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Hủy Lock Mục tiêu</t>
+          <t>Hủy Khóa Mục tiêu</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Sprint/Evade</t>
+          <t>Tăng Tốc/Tránh Né</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Shift trái</t>
+          <t>Shift Trái</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sprint/Evade</t>
+          <t>Tăng Tốc/Tránh Né</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Nhấp chuột phải</t>
+          <t>Nhấp Chuột Phải</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Công cụ thám hiểm</t>
+          <t>Dụng Cụ Thám Hiểm</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Kỹ năng Echo</t>
+          <t>Kỹ Năng Echo</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Bật/Tắt chế độ ngắm</t>
+          <t>Bật/Tắt Chế Độ Ngắm</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Không Gian</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Drop</t>
+          <t>Rơi</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Tăng tốc ngang</t>
+          <t>Trượt Nhanh</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nhấp chuột phải</t>
+          <t>Nhấp Chuột Phải</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 1</t>
+          <t>Đổi sang Thành viên 1</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 2</t>
+          <t>Đổi sang Thành viên 2</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 3</t>
+          <t>Đổi sang Thành viên 3</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Thư</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Bản đồ</t>
+          <t>Bản Đồ</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mở Terminal Nhiệm vụ</t>
+          <t>Mở Thiết Bị Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mở Interface Resonator</t>
+          <t>Mở Giao Diện Resonator</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Mở Wheel Tiện Ích Exploration</t>
+          <t>Mở Bánh Xe Tiện Ích Thám Hiểm</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cấu hình tiện ích khám phá</t>
+          <t>Cài đặt Tiện ích Khám phá</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Tạm Dừng</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Language Text Trong Game</t>
+          <t>Ngôn ngữ văn bản trong game</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Lựa chọn ngôn ngữ</t>
+          <t>Chọn Ngôn Ngữ</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>Tiếng Trung Giản Thể</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tiếng Anh</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>Tiếng Nhật</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Language Lồng Tiếng</t>
+          <t>Ngôn Ngữ Lồng Tiếng</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Lựa chọn ngôn ngữ lồng tiếng</t>
+          <t>Lựa Chọn Ngôn Ngữ Lồng Tiếng</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Tiếng Trung Quốc</t>
+          <t>Tiếng Trung Phổ Thông</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tiếng Anh</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>Tiếng Nhật</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Language Lồng Tiếng</t>
+          <t>Ngôn Ngữ Lồng Tiếng</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Quản lý tệp lồng tiếng</t>
+          <t>Quản Lý File Lồng Tiếng</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Tiếng Trung Quốc</t>
+          <t>Tiếng Trung Phổ Thông</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tiếng Anh</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>Tiếng Nhật</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Thiết Lập</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Thiết Lập</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Âm Thanh</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Graphic</t>
+          <t>Đồ Họa</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Keys</t>
+          <t>Phím</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ngôn Ngữ</t>
         </is>
       </c>
     </row>
